--- a/artfynd/A 5877-2021 artfynd.xlsx
+++ b/artfynd/A 5877-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5877-2021 artfynd.xlsx
+++ b/artfynd/A 5877-2021 artfynd.xlsx
@@ -2787,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117719954</v>
+        <v>117719862</v>
       </c>
       <c r="B20" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452378</v>
+        <v>452365</v>
       </c>
       <c r="R20" t="n">
-        <v>7030139</v>
+        <v>7030096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117719862</v>
+        <v>117719954</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452365</v>
+        <v>452378</v>
       </c>
       <c r="R21" t="n">
-        <v>7030096</v>
+        <v>7030139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5877-2021 artfynd.xlsx
+++ b/artfynd/A 5877-2021 artfynd.xlsx
@@ -2170,7 +2170,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117719829</v>
+        <v>117719724</v>
       </c>
       <c r="B14" t="n">
         <v>79561</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452345</v>
+        <v>452312</v>
       </c>
       <c r="R14" t="n">
-        <v>7030121</v>
+        <v>7030092</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117719854</v>
+        <v>117719829</v>
       </c>
       <c r="B15" t="n">
         <v>79561</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452352</v>
+        <v>452345</v>
       </c>
       <c r="R15" t="n">
-        <v>7030104</v>
+        <v>7030121</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,7 +2374,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117719781</v>
+        <v>117719954</v>
       </c>
       <c r="B16" t="n">
         <v>79562</v>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452336</v>
+        <v>452378</v>
       </c>
       <c r="R16" t="n">
-        <v>7030134</v>
+        <v>7030139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117719787</v>
+        <v>117719781</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2497,21 +2492,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2521,13 +2516,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452341</v>
+        <v>452336</v>
       </c>
       <c r="R17" t="n">
-        <v>7030127</v>
+        <v>7030134</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2583,7 +2578,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117719890</v>
+        <v>117719854</v>
       </c>
       <c r="B18" t="n">
         <v>79561</v>
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452394</v>
+        <v>452352</v>
       </c>
       <c r="R18" t="n">
-        <v>7030091</v>
+        <v>7030104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,6 +2654,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,7 +2685,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117719724</v>
+        <v>117719787</v>
       </c>
       <c r="B19" t="n">
         <v>79561</v>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452312</v>
+        <v>452341</v>
       </c>
       <c r="R19" t="n">
-        <v>7030092</v>
+        <v>7030127</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117719954</v>
+        <v>117719890</v>
       </c>
       <c r="B21" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452378</v>
+        <v>452394</v>
       </c>
       <c r="R21" t="n">
-        <v>7030139</v>
+        <v>7030091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5877-2021 artfynd.xlsx
+++ b/artfynd/A 5877-2021 artfynd.xlsx
@@ -2170,10 +2170,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117719724</v>
+        <v>117719862</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452312</v>
+        <v>452365</v>
       </c>
       <c r="R14" t="n">
-        <v>7030092</v>
+        <v>7030096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117719829</v>
+        <v>117719854</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452345</v>
+        <v>452352</v>
       </c>
       <c r="R15" t="n">
-        <v>7030121</v>
+        <v>7030104</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,10 +2379,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117719954</v>
+        <v>117719781</v>
       </c>
       <c r="B16" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452378</v>
+        <v>452336</v>
       </c>
       <c r="R16" t="n">
-        <v>7030139</v>
+        <v>7030134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2476,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117719781</v>
+        <v>117719740</v>
       </c>
       <c r="B17" t="n">
-        <v>79562</v>
+        <v>79563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,21 +2497,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2516,13 +2521,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452336</v>
+        <v>452312</v>
       </c>
       <c r="R17" t="n">
-        <v>7030134</v>
+        <v>7030107</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2578,10 +2583,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117719854</v>
+        <v>117719890</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452352</v>
+        <v>452394</v>
       </c>
       <c r="R18" t="n">
-        <v>7030104</v>
+        <v>7030091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,11 +2659,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117719787</v>
+        <v>117719724</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452341</v>
+        <v>452312</v>
       </c>
       <c r="R19" t="n">
-        <v>7030127</v>
+        <v>7030092</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117719862</v>
+        <v>117719829</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452365</v>
+        <v>452345</v>
       </c>
       <c r="R20" t="n">
-        <v>7030096</v>
+        <v>7030121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117719890</v>
+        <v>117719787</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452394</v>
+        <v>452341</v>
       </c>
       <c r="R21" t="n">
-        <v>7030091</v>
+        <v>7030127</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117719740</v>
+        <v>117719954</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452312</v>
+        <v>452378</v>
       </c>
       <c r="R22" t="n">
-        <v>7030107</v>
+        <v>7030139</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
